--- a/artfynd/A 3379-2022 artfynd.xlsx
+++ b/artfynd/A 3379-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6901,6 +6901,902 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>110941027</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>551193</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7260998</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>110941061</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>551268</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7261053</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>110941021</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>551233</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7261049</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>110941022</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>551226</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7261023</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>110941026</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>551201</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7261006</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>110941019</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>551246</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7261052</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>110941060</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>551258</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7261054</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>110941020</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>551240</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7261054</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3379-2022 artfynd.xlsx
+++ b/artfynd/A 3379-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3379-2022 artfynd.xlsx
+++ b/artfynd/A 3379-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110941127</v>
+        <v>110941073</v>
       </c>
       <c r="B2" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222741</v>
+        <v>214</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Mörkhövdad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Allocalicium adaequatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Nyl.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550787.3532294596</v>
+        <v>551259</v>
       </c>
       <c r="R2" t="n">
-        <v>7260827.811643491</v>
+        <v>7261053</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110941060</v>
+        <v>110941133</v>
       </c>
       <c r="B3" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2082</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551258</v>
+        <v>551098</v>
       </c>
       <c r="R3" t="n">
-        <v>7261054</v>
+        <v>7260941</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110940964</v>
+        <v>110941089</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550767.4131145758</v>
+        <v>550923</v>
       </c>
       <c r="R4" t="n">
-        <v>7260825.385546367</v>
+        <v>7260812</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110941091</v>
+        <v>110941090</v>
       </c>
       <c r="B5" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551211.4787857262</v>
+        <v>551165</v>
       </c>
       <c r="R5" t="n">
-        <v>7261046.036477123</v>
+        <v>7261004</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110941061</v>
+        <v>110941091</v>
       </c>
       <c r="B6" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2082</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551268</v>
+        <v>551212</v>
       </c>
       <c r="R6" t="n">
-        <v>7261053</v>
+        <v>7261046</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1213,7 @@
         <v>110940962</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551131.5030927367</v>
+        <v>551132</v>
       </c>
       <c r="R7" t="n">
-        <v>7260953.990872363</v>
+        <v>7260954</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110940985</v>
+        <v>110940964</v>
       </c>
       <c r="B8" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551060.1690338075</v>
+        <v>550767</v>
       </c>
       <c r="R8" t="n">
-        <v>7261010.121304046</v>
+        <v>7260825</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110941101</v>
+        <v>110940965</v>
       </c>
       <c r="B9" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551173.4259228957</v>
+        <v>551213</v>
       </c>
       <c r="R9" t="n">
-        <v>7260984.663295291</v>
+        <v>7261042</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110941021</v>
+        <v>110941002</v>
       </c>
       <c r="B10" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551233</v>
+        <v>551060</v>
       </c>
       <c r="R10" t="n">
-        <v>7261048</v>
+        <v>7261010</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110940972</v>
+        <v>110941003</v>
       </c>
       <c r="B11" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,39 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550973.6061278284</v>
+        <v>551068</v>
       </c>
       <c r="R11" t="n">
-        <v>7260961.207097509</v>
+        <v>7261008</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110941100</v>
+        <v>110941004</v>
       </c>
       <c r="B12" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551140.4107674799</v>
+        <v>551082</v>
       </c>
       <c r="R12" t="n">
-        <v>7260968.284140497</v>
+        <v>7260993</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110941114</v>
+        <v>110941005</v>
       </c>
       <c r="B13" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551185.9109028459</v>
+        <v>551073</v>
       </c>
       <c r="R13" t="n">
-        <v>7261008.582541218</v>
+        <v>7260978</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,37 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110941067</v>
+        <v>110941006</v>
       </c>
       <c r="B14" t="n">
-        <v>95532</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550801.3872893023</v>
+        <v>551086</v>
       </c>
       <c r="R14" t="n">
-        <v>7260834.709000452</v>
+        <v>7260949</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110940986</v>
+        <v>110941019</v>
       </c>
       <c r="B15" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2082</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551084.9592709373</v>
+        <v>551245</v>
       </c>
       <c r="R15" t="n">
-        <v>7260949.433350388</v>
+        <v>7261052</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,37 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110941102</v>
+        <v>110941020</v>
       </c>
       <c r="B16" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2082</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551183.8593375685</v>
+        <v>551240</v>
       </c>
       <c r="R16" t="n">
-        <v>7261006.883380447</v>
+        <v>7261053</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110941022</v>
+        <v>110941021</v>
       </c>
       <c r="B17" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551226</v>
+        <v>551233</v>
       </c>
       <c r="R17" t="n">
-        <v>7261023</v>
+        <v>7261048</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,37 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110941094</v>
+        <v>110941022</v>
       </c>
       <c r="B18" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>2082</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551225.6493503592</v>
+        <v>551226</v>
       </c>
       <c r="R18" t="n">
-        <v>7261021.337943261</v>
+        <v>7261023</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2584,37 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110941113</v>
+        <v>110941023</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2082</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551139.5784622584</v>
+        <v>551220</v>
       </c>
       <c r="R19" t="n">
-        <v>7260968.269551521</v>
+        <v>7261009</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,55 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110940968</v>
+        <v>110941024</v>
       </c>
       <c r="B20" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2082</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551147.5436584682</v>
+        <v>551217</v>
       </c>
       <c r="R20" t="n">
-        <v>7260965.082797484</v>
+        <v>7261009</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,15 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110941027</v>
+        <v>110941025</v>
       </c>
       <c r="B21" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551193</v>
+        <v>551209</v>
       </c>
       <c r="R21" t="n">
-        <v>7260998</v>
+        <v>7261008</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,37 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110941111</v>
+        <v>110941026</v>
       </c>
       <c r="B22" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2082</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551083.6744151703</v>
+        <v>551201</v>
       </c>
       <c r="R22" t="n">
-        <v>7260951.489851493</v>
+        <v>7261006</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,59 +2922,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110940980</v>
+        <v>110941027</v>
       </c>
       <c r="B23" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2082</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550873.7877917455</v>
+        <v>551193</v>
       </c>
       <c r="R23" t="n">
-        <v>7260788.983054731</v>
+        <v>7260998</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,55 +3029,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110940970</v>
+        <v>110941028</v>
       </c>
       <c r="B24" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2082</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550839.6065611959</v>
+        <v>551177</v>
       </c>
       <c r="R24" t="n">
-        <v>7260815.415532937</v>
+        <v>7260984</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3238,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,15 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110941131</v>
+        <v>110941029</v>
       </c>
       <c r="B25" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>2082</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3315,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>551074.4621738992</v>
+        <v>551170</v>
       </c>
       <c r="R25" t="n">
-        <v>7260978.355405289</v>
+        <v>7260978</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3350,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3360,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,37 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110941099</v>
+        <v>110941030</v>
       </c>
       <c r="B26" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>2082</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3427,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550978.6217592343</v>
+        <v>551128</v>
       </c>
       <c r="R26" t="n">
-        <v>7260960.047338871</v>
+        <v>7260950</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3462,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,15 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110941020</v>
+        <v>110941031</v>
       </c>
       <c r="B27" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>551240</v>
+        <v>551113</v>
       </c>
       <c r="R27" t="n">
-        <v>7261053</v>
+        <v>7260934</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3574,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3584,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,37 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110941110</v>
+        <v>110941032</v>
       </c>
       <c r="B28" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2082</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550820.0828559938</v>
+        <v>551106</v>
       </c>
       <c r="R28" t="n">
-        <v>7260765.176901903</v>
+        <v>7260929</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3686,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,37 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110941006</v>
+        <v>110941033</v>
       </c>
       <c r="B29" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>551085.7915814756</v>
+        <v>551102</v>
       </c>
       <c r="R29" t="n">
-        <v>7260949.447923761</v>
+        <v>7260925</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3798,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3808,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3835,15 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110941026</v>
+        <v>110941034</v>
       </c>
       <c r="B30" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>551201</v>
+        <v>551092</v>
       </c>
       <c r="R30" t="n">
-        <v>7261006</v>
+        <v>7260923</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3910,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3920,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3947,55 +3778,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110940974</v>
+        <v>110941035</v>
       </c>
       <c r="B31" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2082</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>551187.9697586229</v>
+        <v>551081</v>
       </c>
       <c r="R31" t="n">
-        <v>7261009.866038773</v>
+        <v>7260907</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4027,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4037,12 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4069,15 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110941073</v>
+        <v>110941036</v>
       </c>
       <c r="B32" t="n">
-        <v>76877</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>214</v>
+        <v>2082</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörkhövdad spiklav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Allocalicium adaequatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) M.Prieto &amp; Wedin</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4109,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>551258.4005351382</v>
+        <v>551067</v>
       </c>
       <c r="R32" t="n">
-        <v>7261052.681503622</v>
+        <v>7260916</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4144,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4154,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4181,37 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110941005</v>
+        <v>110941060</v>
       </c>
       <c r="B33" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4221,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>551072.3814181939</v>
+        <v>551258</v>
       </c>
       <c r="R33" t="n">
-        <v>7260978.318980305</v>
+        <v>7261054</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4256,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4266,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4293,15 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110941128</v>
+        <v>110941061</v>
       </c>
       <c r="B34" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4309,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222741</v>
+        <v>2082</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4333,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550822.1492817929</v>
+        <v>551268</v>
       </c>
       <c r="R34" t="n">
-        <v>7260766.044542955</v>
+        <v>7261053</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4368,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4378,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4405,55 +4206,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110940998</v>
+        <v>110941110</v>
       </c>
       <c r="B35" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>551131.4666687252</v>
+        <v>550820</v>
       </c>
       <c r="R35" t="n">
-        <v>7260956.069229951</v>
+        <v>7260765</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4485,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4495,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4522,37 +4313,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110941019</v>
+        <v>110941111</v>
       </c>
       <c r="B36" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2082</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4562,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>551245</v>
+        <v>551084</v>
       </c>
       <c r="R36" t="n">
-        <v>7261052</v>
+        <v>7260952</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4597,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4607,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,37 +4420,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>110941090</v>
+        <v>110941112</v>
       </c>
       <c r="B37" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4674,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>551165.1691641568</v>
+        <v>551098</v>
       </c>
       <c r="R37" t="n">
-        <v>7261004.476584359</v>
+        <v>7260941</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4709,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4719,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,37 +4527,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>110940960</v>
+        <v>110941113</v>
       </c>
       <c r="B38" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4786,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550860.4370114403</v>
+        <v>551139</v>
       </c>
       <c r="R38" t="n">
-        <v>7260814.531111397</v>
+        <v>7260968</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4821,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4858,55 +4634,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110940975</v>
+        <v>110941114</v>
       </c>
       <c r="B39" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>551209.5367011502</v>
+        <v>551186</v>
       </c>
       <c r="R39" t="n">
-        <v>7261038.102429666</v>
+        <v>7261009</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4938,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4948,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,15 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>110940965</v>
+        <v>110940960</v>
       </c>
       <c r="B40" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4991,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5015,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551212.3840325382</v>
+        <v>550861</v>
       </c>
       <c r="R40" t="n">
-        <v>7261041.894497525</v>
+        <v>7260815</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5050,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5087,59 +4848,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110941086</v>
+        <v>110941063</v>
       </c>
       <c r="B41" t="n">
-        <v>55611</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551065.1773437195</v>
+        <v>550864</v>
       </c>
       <c r="R41" t="n">
-        <v>7261009.377378394</v>
+        <v>7260751</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5171,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5181,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,37 +4955,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110941133</v>
+        <v>110940984</v>
       </c>
       <c r="B42" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5248,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551098.0202443013</v>
+        <v>550893</v>
       </c>
       <c r="R42" t="n">
-        <v>7260940.514460259</v>
+        <v>7260898</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5283,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5293,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5320,15 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110941130</v>
+        <v>110940985</v>
       </c>
       <c r="B43" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5336,21 +5073,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5360,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551066.8783086645</v>
+        <v>551060</v>
       </c>
       <c r="R43" t="n">
-        <v>7261007.328194703</v>
+        <v>7261010</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5395,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5405,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5432,55 +5169,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110940973</v>
+        <v>110940986</v>
       </c>
       <c r="B44" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551077.3388463358</v>
+        <v>551085</v>
       </c>
       <c r="R44" t="n">
-        <v>7260980.484742855</v>
+        <v>7260950</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5512,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5522,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5549,37 +5276,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110941098</v>
+        <v>110941130</v>
       </c>
       <c r="B45" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5589,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550867.5772001552</v>
+        <v>551067</v>
       </c>
       <c r="R45" t="n">
-        <v>7260810.913222598</v>
+        <v>7261007</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5624,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5634,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5661,15 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110940984</v>
+        <v>110941131</v>
       </c>
       <c r="B46" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5701,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550893.5365440539</v>
+        <v>551074</v>
       </c>
       <c r="R46" t="n">
-        <v>7260897.854836991</v>
+        <v>7260978</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5736,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5746,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5773,50 +5490,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110941112</v>
+        <v>110940997</v>
       </c>
       <c r="B47" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551098.0202443013</v>
+        <v>551146</v>
       </c>
       <c r="R47" t="n">
-        <v>7260940.514460259</v>
+        <v>7260965</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5848,7 +5565,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5575,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5885,50 +5602,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>110941097</v>
+        <v>110940998</v>
       </c>
       <c r="B48" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550873.8965118367</v>
+        <v>551132</v>
       </c>
       <c r="R48" t="n">
-        <v>7260782.747623265</v>
+        <v>7260956</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5960,7 +5677,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5970,7 +5687,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5997,15 +5714,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110941003</v>
+        <v>110940968</v>
       </c>
       <c r="B49" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,34 +5725,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>551068.1121980638</v>
+        <v>551147</v>
       </c>
       <c r="R49" t="n">
-        <v>7261008.181375185</v>
+        <v>7260965</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6072,7 +5789,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +5799,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6109,50 +5826,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110940992</v>
+        <v>110940970</v>
       </c>
       <c r="B50" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550801.3872893023</v>
+        <v>550840</v>
       </c>
       <c r="R50" t="n">
-        <v>7260834.709000452</v>
+        <v>7260816</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6184,7 +5901,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6194,7 +5911,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6221,50 +5938,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>110941129</v>
+        <v>110940971</v>
       </c>
       <c r="B51" t="n">
-        <v>95674</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222741</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550896.5149433318</v>
+        <v>550918</v>
       </c>
       <c r="R51" t="n">
-        <v>7260894.164535476</v>
+        <v>7260931</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6296,7 +6013,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6306,7 +6023,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6333,15 +6050,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110940997</v>
+        <v>110940972</v>
       </c>
       <c r="B52" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,16 +6061,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6369,7 +6081,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6378,10 +6090,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>551145.4628931064</v>
+        <v>550973</v>
       </c>
       <c r="R52" t="n">
-        <v>7260965.046320412</v>
+        <v>7260961</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6413,7 +6125,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6423,7 +6135,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6450,15 +6162,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110941004</v>
+        <v>110940973</v>
       </c>
       <c r="B53" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6466,34 +6173,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>551082.1070445151</v>
+        <v>551077</v>
       </c>
       <c r="R53" t="n">
-        <v>7260993.457849125</v>
+        <v>7260980</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6525,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6535,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6562,15 +6274,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>110941002</v>
+        <v>110940974</v>
       </c>
       <c r="B54" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6578,34 +6285,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Abraham-Persbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>551060.1690338075</v>
+        <v>551188</v>
       </c>
       <c r="R54" t="n">
-        <v>7261010.121304046</v>
+        <v>7261010</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6637,7 +6349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6647,7 +6359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,15 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>110940971</v>
+        <v>110940975</v>
       </c>
       <c r="B55" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6710,7 +6422,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6719,10 +6431,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550917.9259425686</v>
+        <v>551209</v>
       </c>
       <c r="R55" t="n">
-        <v>7260931.544670393</v>
+        <v>7261038</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6754,7 +6466,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6764,7 +6476,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6788,6 +6500,880 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>110941086</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>551065</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7261009</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>110940980</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>550874</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7260789</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>110941134</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>551043</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7260989</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>110941067</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>550801</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7260835</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>110940992</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>550801</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7260835</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>110941127</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>550787</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7260828</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>110941128</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>550822</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7260766</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>110941129</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>550897</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7260894</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
